--- a/projetPFA/outputs/test_Machines_Test_Realiste.xlsx
+++ b/projetPFA/outputs/test_Machines_Test_Realiste.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Lignes_utiles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Lignes_rejetees" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +471,7 @@
         <v>3.68</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +497,7 @@
         <v>1.99</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +523,7 @@
         <v>6.48</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -550,7 +549,7 @@
         <v>7.18</v>
       </c>
       <c r="F5" t="n">
-        <v>0.925</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +575,7 @@
         <v>4.73</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="7">
@@ -628,7 +627,7 @@
         <v>1.87</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="9">
@@ -680,7 +679,7 @@
         <v>14.78</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +731,7 @@
         <v>11.07</v>
       </c>
       <c r="F12" t="n">
-        <v>0.845</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="13">
@@ -784,7 +783,7 @@
         <v>3.93</v>
       </c>
       <c r="F14" t="n">
-        <v>0.985</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="15">
@@ -810,7 +809,7 @@
         <v>4.67</v>
       </c>
       <c r="F15" t="n">
-        <v>0.995</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="16">
@@ -888,7 +887,7 @@
         <v>8.19</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="19">
@@ -914,7 +913,7 @@
         <v>0.09</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="20">
@@ -966,7 +965,7 @@
         <v>7.29</v>
       </c>
       <c r="F21" t="n">
-        <v>0.93</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="22">
@@ -992,7 +991,7 @@
         <v>10.7</v>
       </c>
       <c r="F22" t="n">
-        <v>0.885</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
@@ -1018,7 +1017,7 @@
         <v>2.51</v>
       </c>
       <c r="F23" t="n">
-        <v>0.975</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="24">
@@ -1044,7 +1043,7 @@
         <v>8.66</v>
       </c>
       <c r="F24" t="n">
-        <v>0.975</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1070,7 +1069,7 @@
         <v>1.87</v>
       </c>
       <c r="F25" t="n">
-        <v>0.975</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="26">
@@ -1200,7 +1199,7 @@
         <v>8.42</v>
       </c>
       <c r="F30" t="n">
-        <v>0.895</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="31">
@@ -1330,7 +1329,7 @@
         <v>6.39</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="36">
@@ -1408,7 +1407,7 @@
         <v>14.71</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="39">
@@ -1434,7 +1433,7 @@
         <v>12.94</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1486,7 +1485,7 @@
         <v>1.36</v>
       </c>
       <c r="F41" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1564,7 +1563,7 @@
         <v>11.18</v>
       </c>
       <c r="F44" t="n">
-        <v>0.995</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="45">
@@ -1642,7 +1641,7 @@
         <v>18.65</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="48">
@@ -1668,7 +1667,7 @@
         <v>7.51</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="49">
@@ -1772,7 +1771,7 @@
         <v>2.84</v>
       </c>
       <c r="F52" t="n">
-        <v>0.98</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="53">
@@ -1798,7 +1797,7 @@
         <v>7.65</v>
       </c>
       <c r="F53" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="54">
@@ -1824,7 +1823,7 @@
         <v>11.13</v>
       </c>
       <c r="F54" t="n">
-        <v>0.97</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="55">
@@ -1876,7 +1875,7 @@
         <v>4.25</v>
       </c>
       <c r="F56" t="n">
-        <v>0.99</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="57">
@@ -1902,7 +1901,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="58">
@@ -1954,7 +1953,7 @@
         <v>6.56</v>
       </c>
       <c r="F59" t="n">
-        <v>0.945</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2006,7 +2005,7 @@
         <v>4.11</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="62">
@@ -2084,7 +2083,7 @@
         <v>8.99</v>
       </c>
       <c r="F64" t="n">
-        <v>0.995</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="65">
@@ -2110,7 +2109,7 @@
         <v>8.66</v>
       </c>
       <c r="F65" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="66">
@@ -2136,7 +2135,7 @@
         <v>10.71</v>
       </c>
       <c r="F66" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="67">
@@ -2162,7 +2161,7 @@
         <v>9.859999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>0.995</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="68">
@@ -2188,7 +2187,7 @@
         <v>7.74</v>
       </c>
       <c r="F68" t="n">
-        <v>0.975</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="69">
@@ -2344,7 +2343,7 @@
         <v>7.57</v>
       </c>
       <c r="F74" t="n">
-        <v>0.905</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="75">
@@ -2396,7 +2395,7 @@
         <v>9.289999999999999</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="77">
@@ -2448,460 +2447,6 @@
         <v>6.92</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Machine</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>HeuresFonctionnement</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>TauxDefaut_%</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>utilite_predite</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>score_confiance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Assembly board to board_991014</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Station de vissage_335552</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SMC Adaptor_148458</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Optimel Ferite_397571</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Presse hydraulique_598216</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Assembly board to board_451470</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Presse hydraulique_805477</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Presse hydraulique_254511</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Optimel Ferite_577538</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>E-Test Leshin_790855</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Camera inspection_161483</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4308.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0.555</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Optimel Ferite_958179</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E13" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Testeur fonctionnel_796101</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BTB</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>3826.9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Non_utile</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
         <v>1</v>
       </c>
     </row>
